--- a/src/pyuniclass/data/Uniclass2015_FI_v1_5.xlsx
+++ b/src/pyuniclass/data/Uniclass2015_FI_v1_5.xlsx
@@ -1,28 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BrookA\source\repos\NBS.Uniclass.Publishing\src\NBS.Uniclass.Publishing\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KharinA\Dev\repos\nbs-uniclass-infrastructure\s3-contents\downloads\uniclass-all-2025-07\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8898CAEE-C96D-45B8-9506-9753E5D9BA1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FEE743F-10E1-4DDA-B79A-D1A732CFF98C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FI" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="145621" fullCalcOnLoad="1"/>
+  <calcPr calcId="145621"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="342">
-  <si>
-    <t>FI Form of information - April 2024 - v1.5</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="342">
+  <si>
+    <t>FI Form of information - July 2025 - v1.5</t>
   </si>
   <si>
     <t>Code</t>
@@ -1052,8 +1052,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1100,6 +1099,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1137,22 +1143,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="7">
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="1" applyBorder="1" xfId="1" applyProtection="1"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="2" applyFill="1" borderId="1" applyBorder="1" xfId="1" applyProtection="1" applyAlignment="1">
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="3" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="3" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="4" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="5" applyFont="1" fillId="2" applyFill="1" borderId="1" applyBorder="1" xfId="1" applyProtection="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1161,6 +1166,17 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="19">
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1179,17 +1195,6 @@
         <scheme val="minor"/>
       </font>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-      </font>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1420,8 +1425,8 @@
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="NRM1" dataDxfId="3"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="IFC 2x3 TC1" dataDxfId="2"/>
     <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="IFC 4Add2 TC1"/>
-    <tableColumn id="14" xr3:uid="{7E231B53-0F11-45EB-B058-B4DD7CE438CD}" name="IFC 4x3Add2 TC1" dataDxfId="0"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="CESMM" dataDxfId="1"/>
+    <tableColumn id="14" xr3:uid="{7E231B53-0F11-45EB-B058-B4DD7CE438CD}" name="IFC 4x3Add2 TC1" dataDxfId="1"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="CESMM" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="NBS" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1717,1649 +1722,1650 @@
   <dimension ref="A1:N97"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.85546875" customWidth="1" style="3"/>
-    <col min="2" max="6" width="12" customWidth="1" style="3"/>
-    <col min="7" max="7" width="71.42578125" customWidth="1" style="3"/>
-    <col min="8" max="8" width="21.5703125" customWidth="1" style="3"/>
-    <col min="9" max="9" width="19" customWidth="1" style="3"/>
-    <col min="10" max="12" width="12" customWidth="1" style="3"/>
-    <col min="13" max="13" width="12.7109375" customWidth="1" style="3"/>
-    <col min="14" max="14" width="13" customWidth="1" style="3"/>
-    <col min="15" max="16384" width="9.140625" customWidth="1" style="3"/>
+    <col min="1" max="1" width="18.85546875" style="2" customWidth="1"/>
+    <col min="2" max="6" width="12" style="2" customWidth="1"/>
+    <col min="7" max="7" width="71.42578125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="21.5703125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="19" style="2" customWidth="1"/>
+    <col min="10" max="12" width="12" style="2" customWidth="1"/>
+    <col min="13" max="13" width="12.7109375" style="2" customWidth="1"/>
+    <col min="14" max="14" width="13" style="2" customWidth="1"/>
+    <col min="15" max="15" width="9.140625" style="2" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="39.75" customHeight="1">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:14" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-    </row>
-    <row r="2" ht="3" customHeight="1"/>
-    <row r="3" ht="37.5" customHeight="1">
-      <c r="A3" s="5" t="s">
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="3" customHeight="1" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="J3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="K3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="L3" s="5" t="s">
+      <c r="L3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="M3" s="5" t="s">
+      <c r="M3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="N3" s="5" t="s">
+      <c r="N3" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="I4" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H5" s="4"/>
-      <c r="I5" s="3" t="s">
+      <c r="H5" s="3"/>
+      <c r="I5" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="3" t="s">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="G6" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="I6" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="3" t="s">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="I7" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="3" t="s">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="G8" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="I8" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="3" t="s">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="G9" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="I9" s="3" t="s">
+      <c r="I9" s="2" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="3" t="s">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="G10" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="I10" s="3" t="s">
+      <c r="I10" s="2" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="3" t="s">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="G11" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="I11" s="3" t="s">
+      <c r="I11" s="2" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="3" t="s">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="G12" s="3" t="s">
+      <c r="G12" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="I12" s="3" t="s">
+      <c r="I12" s="2" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="3" t="s">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="G13" s="3" t="s">
+      <c r="G13" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="I13" s="3" t="s">
+      <c r="I13" s="2" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="3" t="s">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="G14" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="I14" s="3" t="s">
+      <c r="I14" s="2" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="3" t="s">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="G15" s="3" t="s">
+      <c r="G15" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="I15" s="3" t="s">
+      <c r="I15" s="2" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="3" t="s">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="G16" s="3" t="s">
+      <c r="G16" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="I16" s="3" t="s">
+      <c r="I16" s="2" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="3" t="s">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="G17" s="3" t="s">
+      <c r="G17" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="I17" s="3" t="s">
+      <c r="I17" s="2" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="3" t="s">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="G18" s="3" t="s">
+      <c r="G18" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="I18" s="3" t="s">
+      <c r="I18" s="2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="3" t="s">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="G19" s="3" t="s">
+      <c r="G19" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="I19" s="3" t="s">
+      <c r="I19" s="2" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="3" t="s">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="G20" s="3" t="s">
+      <c r="G20" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="I20" s="3" t="s">
+      <c r="I20" s="2" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="3" t="s">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C21" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="G21" s="3" t="s">
+      <c r="G21" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="I21" s="3" t="s">
+      <c r="I21" s="2" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="3" t="s">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C22" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="G22" s="3" t="s">
+      <c r="G22" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="I22" s="3" t="s">
+      <c r="I22" s="2" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="3" t="s">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="G23" s="3" t="s">
+      <c r="G23" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="I23" s="3" t="s">
+      <c r="I23" s="2" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="3" t="s">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C24" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="G24" s="3" t="s">
+      <c r="G24" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="I24" s="3" t="s">
+      <c r="I24" s="2" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="3" t="s">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="C25" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="G25" s="3" t="s">
+      <c r="G25" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="I25" s="3" t="s">
+      <c r="I25" s="2" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="3" t="s">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C26" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="G26" s="3" t="s">
+      <c r="G26" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="I26" s="3" t="s">
+      <c r="I26" s="2" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="3" t="s">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B27" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="C27" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="G27" s="3" t="s">
+      <c r="G27" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="I27" s="3" t="s">
+      <c r="I27" s="2" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="3" t="s">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="C28" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="G28" s="3" t="s">
+      <c r="G28" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="I28" s="3" t="s">
+      <c r="I28" s="2" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="3" t="s">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="C29" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="G29" s="3" t="s">
+      <c r="G29" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="I29" s="3" t="s">
+      <c r="I29" s="2" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="3" t="s">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="C30" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="G30" s="3" t="s">
+      <c r="G30" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="I30" s="3" t="s">
+      <c r="I30" s="2" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="3" t="s">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B31" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="C31" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="G31" s="3" t="s">
+      <c r="G31" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="I31" s="3" t="s">
+      <c r="I31" s="2" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="3" t="s">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B32" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="G32" s="3" t="s">
+      <c r="G32" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="I32" s="3" t="s">
+      <c r="I32" s="2" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="3" t="s">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B33" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="C33" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="G33" s="3" t="s">
+      <c r="G33" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="I33" s="3" t="s">
+      <c r="I33" s="2" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="3" t="s">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B34" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="C34" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="G34" s="3" t="s">
+      <c r="G34" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="I34" s="3" t="s">
+      <c r="I34" s="2" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="3" t="s">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B35" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="C35" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="G35" s="3" t="s">
+      <c r="G35" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="I35" s="3" t="s">
+      <c r="I35" s="2" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="3" t="s">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B36" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="C36" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="G36" s="3" t="s">
+      <c r="G36" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="I36" s="3" t="s">
+      <c r="I36" s="2" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="3" t="s">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B37" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="C37" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="G37" s="3" t="s">
+      <c r="G37" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="I37" s="3" t="s">
+      <c r="I37" s="2" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="3" t="s">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="B38" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="G38" s="3" t="s">
+      <c r="G38" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="I38" s="3" t="s">
+      <c r="I38" s="2" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="3" t="s">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="B39" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="C39" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G39" s="3" t="s">
+      <c r="G39" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="I39" s="3" t="s">
+      <c r="I39" s="2" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="3" t="s">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="B40" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="C40" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="G40" s="3" t="s">
+      <c r="G40" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="I40" s="3" t="s">
+      <c r="I40" s="2" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="3" t="s">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="B41" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="C41" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="G41" s="3" t="s">
+      <c r="G41" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="I41" s="3" t="s">
+      <c r="I41" s="2" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="3" t="s">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="B42" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="G42" s="3" t="s">
+      <c r="G42" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="I42" s="3" t="s">
+      <c r="I42" s="2" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="3" t="s">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="B43" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C43" s="3" t="s">
+      <c r="C43" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G43" s="3" t="s">
+      <c r="G43" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="I43" s="3" t="s">
+      <c r="I43" s="2" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="3" t="s">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="B44" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C44" s="3" t="s">
+      <c r="C44" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="G44" s="3" t="s">
+      <c r="G44" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="I44" s="3" t="s">
+      <c r="I44" s="2" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="3" t="s">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="B45" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C45" s="3" t="s">
+      <c r="C45" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G45" s="3" t="s">
+      <c r="G45" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="I45" s="3" t="s">
+      <c r="I45" s="2" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="3" t="s">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="B46" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C46" s="3" t="s">
+      <c r="C46" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="G46" s="3" t="s">
+      <c r="G46" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="I46" s="3" t="s">
+      <c r="I46" s="2" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="3" t="s">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="B47" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C47" s="3" t="s">
+      <c r="C47" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="G47" s="3" t="s">
+      <c r="G47" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="I47" s="3" t="s">
+      <c r="I47" s="2" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="3" t="s">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="B48" s="3" t="s">
+      <c r="B48" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="G48" s="3" t="s">
+      <c r="G48" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="I48" s="3" t="s">
+      <c r="I48" s="2" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="3" t="s">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="B49" s="3" t="s">
+      <c r="B49" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C49" s="3" t="s">
+      <c r="C49" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="G49" s="3" t="s">
+      <c r="G49" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="I49" s="3" t="s">
+      <c r="I49" s="2" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="3" t="s">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="B50" s="3" t="s">
+      <c r="B50" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C50" s="3" t="s">
+      <c r="C50" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="G50" s="3" t="s">
+      <c r="G50" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="I50" s="3" t="s">
+      <c r="I50" s="2" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="3" t="s">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A51" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="B51" s="3" t="s">
+      <c r="B51" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C51" s="3" t="s">
+      <c r="C51" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="G51" s="3" t="s">
+      <c r="G51" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="I51" s="3" t="s">
+      <c r="I51" s="2" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="3" t="s">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="B52" s="3" t="s">
+      <c r="B52" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C52" s="3" t="s">
+      <c r="C52" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="G52" s="3" t="s">
+      <c r="G52" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="I52" s="3" t="s">
+      <c r="I52" s="2" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="3" t="s">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A53" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="B53" s="3" t="s">
+      <c r="B53" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C53" s="3" t="s">
+      <c r="C53" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="G53" s="3" t="s">
+      <c r="G53" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="I53" s="3" t="s">
+      <c r="I53" s="2" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="3" t="s">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="B54" s="3" t="s">
+      <c r="B54" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C54" s="3" t="s">
+      <c r="C54" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="G54" s="3" t="s">
+      <c r="G54" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="I54" s="3" t="s">
+      <c r="I54" s="2" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="3" t="s">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A55" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="B55" s="3" t="s">
+      <c r="B55" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C55" s="3" t="s">
+      <c r="C55" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="G55" s="3" t="s">
+      <c r="G55" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="I55" s="3" t="s">
+      <c r="I55" s="2" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="3" t="s">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A56" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="B56" s="3" t="s">
+      <c r="B56" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C56" s="3" t="s">
+      <c r="C56" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="G56" s="3" t="s">
+      <c r="G56" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="I56" s="3" t="s">
+      <c r="I56" s="2" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="3" t="s">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="B57" s="3" t="s">
+      <c r="B57" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C57" s="3" t="s">
+      <c r="C57" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="G57" s="3" t="s">
+      <c r="G57" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="I57" s="3" t="s">
+      <c r="I57" s="2" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="3" t="s">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A58" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="B58" s="3" t="s">
+      <c r="B58" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C58" s="3" t="s">
+      <c r="C58" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="G58" s="3" t="s">
+      <c r="G58" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="I58" s="3" t="s">
+      <c r="I58" s="2" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="3" t="s">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="B59" s="3" t="s">
+      <c r="B59" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C59" s="3" t="s">
+      <c r="C59" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="G59" s="3" t="s">
+      <c r="G59" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="I59" s="3" t="s">
+      <c r="I59" s="2" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="3" t="s">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="B60" s="3" t="s">
+      <c r="B60" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C60" s="3" t="s">
+      <c r="C60" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="G60" s="3" t="s">
+      <c r="G60" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="I60" s="3" t="s">
+      <c r="I60" s="2" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="3" t="s">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A61" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="B61" s="3" t="s">
+      <c r="B61" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="G61" s="3" t="s">
+      <c r="G61" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="I61" s="3" t="s">
+      <c r="I61" s="2" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="3" t="s">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="B62" s="3" t="s">
+      <c r="B62" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C62" s="3" t="s">
+      <c r="C62" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="G62" s="3" t="s">
+      <c r="G62" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="I62" s="3" t="s">
+      <c r="I62" s="2" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="3" t="s">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="B63" s="3" t="s">
+      <c r="B63" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C63" s="3" t="s">
+      <c r="C63" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="G63" s="3" t="s">
+      <c r="G63" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="I63" s="3" t="s">
+      <c r="I63" s="2" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="3" t="s">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A64" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="B64" s="3" t="s">
+      <c r="B64" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C64" s="3" t="s">
+      <c r="C64" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="G64" s="3" t="s">
+      <c r="G64" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="I64" s="3" t="s">
+      <c r="I64" s="2" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="3" t="s">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A65" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="B65" s="3" t="s">
+      <c r="B65" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="G65" s="3" t="s">
+      <c r="G65" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="I65" s="3" t="s">
+      <c r="I65" s="2" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="3" t="s">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A66" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="B66" s="3" t="s">
+      <c r="B66" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="C66" s="3" t="s">
+      <c r="C66" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="G66" s="3" t="s">
+      <c r="G66" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="I66" s="3" t="s">
+      <c r="I66" s="2" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="3" t="s">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A67" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="B67" s="3" t="s">
+      <c r="B67" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="C67" s="3" t="s">
+      <c r="C67" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="G67" s="3" t="s">
+      <c r="G67" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="I67" s="3" t="s">
+      <c r="I67" s="2" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="3" t="s">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A68" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="B68" s="3" t="s">
+      <c r="B68" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="C68" s="3" t="s">
+      <c r="C68" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="G68" s="3" t="s">
+      <c r="G68" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="I68" s="3" t="s">
+      <c r="I68" s="2" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="3" t="s">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A69" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="B69" s="3" t="s">
+      <c r="B69" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="C69" s="3" t="s">
+      <c r="C69" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="G69" s="3" t="s">
+      <c r="G69" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="I69" s="3" t="s">
+      <c r="I69" s="2" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="3" t="s">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A70" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="B70" s="3" t="s">
+      <c r="B70" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="C70" s="3" t="s">
+      <c r="C70" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="G70" s="3" t="s">
+      <c r="G70" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="I70" s="3" t="s">
+      <c r="I70" s="2" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="3" t="s">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A71" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="B71" s="3" t="s">
+      <c r="B71" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="G71" s="3" t="s">
+      <c r="G71" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="I71" s="3" t="s">
+      <c r="I71" s="2" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="3" t="s">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A72" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="B72" s="3" t="s">
+      <c r="B72" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C72" s="3" t="s">
+      <c r="C72" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="G72" s="3" t="s">
+      <c r="G72" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="I72" s="3" t="s">
+      <c r="I72" s="2" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="3" t="s">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A73" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="B73" s="3" t="s">
+      <c r="B73" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C73" s="3" t="s">
+      <c r="C73" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="G73" s="3" t="s">
+      <c r="G73" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="I73" s="3" t="s">
+      <c r="I73" s="2" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="3" t="s">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A74" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B74" s="3" t="s">
+      <c r="B74" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C74" s="3" t="s">
+      <c r="C74" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="G74" s="3" t="s">
+      <c r="G74" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="I74" s="3" t="s">
+      <c r="I74" s="2" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="3" t="s">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A75" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="B75" s="3" t="s">
+      <c r="B75" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C75" s="3" t="s">
+      <c r="C75" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="G75" s="3" t="s">
+      <c r="G75" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="I75" s="3" t="s">
+      <c r="I75" s="2" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="3" t="s">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A76" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="B76" s="3" t="s">
+      <c r="B76" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C76" s="3" t="s">
+      <c r="C76" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="G76" s="3" t="s">
+      <c r="G76" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="I76" s="3" t="s">
+      <c r="I76" s="2" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="3" t="s">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A77" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="B77" s="3" t="s">
+      <c r="B77" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C77" s="3" t="s">
+      <c r="C77" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="G77" s="3" t="s">
+      <c r="G77" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="I77" s="3" t="s">
+      <c r="I77" s="2" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="3" t="s">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A78" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="B78" s="3" t="s">
+      <c r="B78" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C78" s="3" t="s">
+      <c r="C78" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="G78" s="3" t="s">
+      <c r="G78" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="I78" s="3" t="s">
+      <c r="I78" s="2" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="3" t="s">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A79" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="B79" s="3" t="s">
+      <c r="B79" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C79" s="3" t="s">
+      <c r="C79" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="G79" s="3" t="s">
+      <c r="G79" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="I79" s="3" t="s">
+      <c r="I79" s="2" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="3" t="s">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A80" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="B80" s="3" t="s">
+      <c r="B80" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C80" s="3" t="s">
+      <c r="C80" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="G80" s="3" t="s">
+      <c r="G80" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="I80" s="3" t="s">
+      <c r="I80" s="2" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="3" t="s">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A81" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="B81" s="3" t="s">
+      <c r="B81" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C81" s="3" t="s">
+      <c r="C81" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="G81" s="3" t="s">
+      <c r="G81" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="I81" s="3" t="s">
+      <c r="I81" s="2" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="3" t="s">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A82" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="B82" s="3" t="s">
+      <c r="B82" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C82" s="3" t="s">
+      <c r="C82" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="G82" s="3" t="s">
+      <c r="G82" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="I82" s="3" t="s">
+      <c r="I82" s="2" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="3" t="s">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A83" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="B83" s="3" t="s">
+      <c r="B83" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C83" s="3" t="s">
+      <c r="C83" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="G83" s="3" t="s">
+      <c r="G83" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="I83" s="3" t="s">
+      <c r="I83" s="2" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="3" t="s">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A84" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="B84" s="3" t="s">
+      <c r="B84" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C84" s="3" t="s">
+      <c r="C84" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="G84" s="3" t="s">
+      <c r="G84" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="I84" s="3" t="s">
+      <c r="I84" s="2" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="3" t="s">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A85" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="B85" s="3" t="s">
+      <c r="B85" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C85" s="3" t="s">
+      <c r="C85" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="G85" s="3" t="s">
+      <c r="G85" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="I85" s="3" t="s">
+      <c r="I85" s="2" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="3" t="s">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A86" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="B86" s="3" t="s">
+      <c r="B86" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C86" s="3" t="s">
+      <c r="C86" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="G86" s="3" t="s">
+      <c r="G86" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="I86" s="3" t="s">
+      <c r="I86" s="2" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="3" t="s">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A87" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="B87" s="3" t="s">
+      <c r="B87" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C87" s="3" t="s">
+      <c r="C87" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="G87" s="3" t="s">
+      <c r="G87" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="I87" s="3" t="s">
+      <c r="I87" s="2" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="3" t="s">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A88" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="B88" s="3" t="s">
+      <c r="B88" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C88" s="3" t="s">
+      <c r="C88" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="G88" s="3" t="s">
+      <c r="G88" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="I88" s="3" t="s">
+      <c r="I88" s="2" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="3" t="s">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A89" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="B89" s="3" t="s">
+      <c r="B89" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C89" s="3" t="s">
+      <c r="C89" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="G89" s="3" t="s">
+      <c r="G89" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="I89" s="3" t="s">
+      <c r="I89" s="2" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="3" t="s">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A90" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="B90" s="3" t="s">
+      <c r="B90" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C90" s="3" t="s">
+      <c r="C90" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="G90" s="3" t="s">
+      <c r="G90" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="I90" s="3" t="s">
+      <c r="I90" s="2" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="3" t="s">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A91" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="B91" s="3" t="s">
+      <c r="B91" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C91" s="3" t="s">
+      <c r="C91" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="G91" s="3" t="s">
+      <c r="G91" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="I91" s="3" t="s">
+      <c r="I91" s="2" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="3" t="s">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A92" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="B92" s="3" t="s">
+      <c r="B92" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C92" s="3" t="s">
+      <c r="C92" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="G92" s="3" t="s">
+      <c r="G92" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="I92" s="3" t="s">
+      <c r="I92" s="2" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="3" t="s">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A93" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="B93" s="3" t="s">
+      <c r="B93" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C93" s="3" t="s">
+      <c r="C93" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="G93" s="3" t="s">
+      <c r="G93" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="I93" s="3" t="s">
+      <c r="I93" s="2" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="3" t="s">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A94" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="B94" s="3" t="s">
+      <c r="B94" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C94" s="3" t="s">
+      <c r="C94" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="G94" s="3" t="s">
+      <c r="G94" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="I94" s="3" t="s">
+      <c r="I94" s="2" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="3" t="s">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A95" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="B95" s="3" t="s">
+      <c r="B95" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C95" s="3" t="s">
+      <c r="C95" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="G95" s="3" t="s">
+      <c r="G95" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="I95" s="3" t="s">
+      <c r="I95" s="2" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="3" t="s">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A96" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="B96" s="3" t="s">
+      <c r="B96" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C96" s="3" t="s">
+      <c r="C96" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="G96" s="3" t="s">
+      <c r="G96" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="I96" s="3" t="s">
+      <c r="I96" s="2" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="3" t="s">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A97" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="B97" s="3" t="s">
+      <c r="B97" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C97" s="3" t="s">
+      <c r="C97" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="G97" s="3" t="s">
+      <c r="G97" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="I97" s="3" t="s">
+      <c r="I97" s="2" t="s">
         <v>341</v>
       </c>
     </row>
@@ -3367,9 +3373,8 @@
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>